--- a/results/regionResults.xlsx
+++ b/results/regionResults.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr dateCompatibility="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joshuadimasaka/Desktop/PhD/GitHub/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joshuadimasaka/Desktop/PhD/GitHub/M78MaasimSaranganiEarthquakeRisk/results/expectedN/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AE7A4A8-CE2B-E141-865B-E4C30161D696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{61C0F0FE-F43E-0242-B8B7-06A16D36E4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2640" windowWidth="27640" windowHeight="16940" xr2:uid="{4E6CF924-3F5B-3C4B-9818-FD46B1D58A56}"/>
+    <workbookView xWindow="60" yWindow="760" windowWidth="25780" windowHeight="10600" xr2:uid="{0FFD5A7A-669E-B646-BB2D-03467834916D}"/>
   </bookViews>
   <sheets>
     <sheet name="adm1_risk" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -33,15 +36,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="11" uniqueCount="11">
+  <si>
+    <t>adm1_psgc</t>
+  </si>
+  <si>
+    <t>adm1_en</t>
+  </si>
   <si>
     <t>Region XI (Davao Region)</t>
   </si>
   <si>
     <t>Region XII (SOCCSKSARGEN)</t>
-  </si>
-  <si>
-    <t>Region</t>
   </si>
   <si>
     <t>Average Severe Damage Probability</t>
@@ -55,11 +61,20 @@
   <si>
     <t>High-Risk Concentration (Top 10%)</t>
   </si>
+  <si>
+    <t>Expected number of damaged buildings</t>
+  </si>
+  <si>
+    <t>Expected number of severely damaged buildings</t>
+  </si>
+  <si>
+    <t>Expected number of collapsed buildings</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -383,15 +398,15 @@
   </fills>
   <borders count="10">
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="thick">
         <color theme="4"/>
@@ -399,8 +414,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="thick">
         <color theme="4" tint="0.499984740745262"/>
@@ -408,8 +423,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.39997558519241921"/>
@@ -417,12 +432,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <start style="thin">
         <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
+      </start>
+      <end style="thin">
         <color rgb="FF7F7F7F"/>
-      </right>
+      </end>
       <top style="thin">
         <color rgb="FF7F7F7F"/>
       </top>
@@ -432,12 +447,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <start style="thin">
         <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
+      </start>
+      <end style="thin">
         <color rgb="FF3F3F3F"/>
-      </right>
+      </end>
       <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
@@ -447,8 +462,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -456,12 +471,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <start style="double">
         <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
+      </start>
+      <end style="double">
         <color rgb="FF3F3F3F"/>
-      </right>
+      </end>
       <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
@@ -471,12 +486,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <start style="thin">
         <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
+      </start>
+      <end style="thin">
         <color rgb="FFB2B2B2"/>
-      </right>
+      </end>
       <top style="thin">
         <color rgb="FFB2B2B2"/>
       </top>
@@ -486,8 +501,8 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <start/>
+      <end/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -543,10 +558,26 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="21" builtinId="30" customBuiltin="1"/>
@@ -608,7 +639,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -761,25 +792,25 @@
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
+            <a:gs pos="0%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:lumMod val="110%"/>
+                <a:satMod val="105%"/>
+                <a:tint val="67%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="50%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:lumMod val="105%"/>
+                <a:satMod val="103%"/>
+                <a:tint val="73%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100000">
+            <a:gs pos="100%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:lumMod val="105%"/>
+                <a:satMod val="109%"/>
+                <a:tint val="81%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -787,25 +818,25 @@
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
+            <a:gs pos="0%">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:satMod val="103%"/>
+                <a:lumMod val="102%"/>
+                <a:tint val="94%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="50%">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:satMod val="110%"/>
+                <a:lumMod val="100%"/>
+                <a:shade val="100%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100000">
+            <a:gs pos="100%">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:lumMod val="99%"/>
+                <a:satMod val="120%"/>
+                <a:shade val="78%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -818,21 +849,21 @@
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter lim="800%"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter lim="800%"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:miter lim="800%"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -846,7 +877,7 @@
           <a:effectLst>
             <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="63%"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -858,32 +889,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
+            <a:tint val="95%"/>
+            <a:satMod val="170%"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
-            <a:gs pos="0">
+            <a:gs pos="0%">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="93%"/>
+                <a:satMod val="150%"/>
+                <a:shade val="98%"/>
+                <a:lumMod val="102%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="50%">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="98%"/>
+                <a:satMod val="130%"/>
+                <a:shade val="90%"/>
+                <a:lumMod val="103%"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100000">
+            <a:gs pos="100%">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="63%"/>
+                <a:satMod val="120%"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -923,25 +954,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A199CB19-07BE-C244-825F-C6FBA8503128}">
-  <dimension ref="A1:E3"/>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF004E-237E-5F46-A9B4-C1F5A869EF40}">
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13" customWidth="1"/>
+    <col min="3" max="9" width="13" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:9" ht="85" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -950,39 +978,75 @@
       <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1100000000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4">
         <v>1.87521240087671E-2</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D2" s="4">
         <v>1.35646706350523E-3</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="5">
         <v>697</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="4">
         <v>3.3092286648520503E-4</v>
       </c>
+      <c r="G2" s="5">
+        <v>85565.855136686994</v>
+      </c>
+      <c r="H2" s="5">
+        <v>64913.777036719897</v>
+      </c>
+      <c r="I2" s="5">
+        <v>2857.03297963369</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1200000000</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4">
         <v>0.105920702439618</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="4">
         <v>8.7997575557527893E-3</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="5">
         <v>401516</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="4">
         <v>0.211765462877649</v>
+      </c>
+      <c r="G3" s="5">
+        <v>421547.79360299901</v>
+      </c>
+      <c r="H3" s="5">
+        <v>340395.32357774401</v>
+      </c>
+      <c r="I3" s="5">
+        <v>16684.7011157671</v>
       </c>
     </row>
   </sheetData>
